--- a/Excel/EquipQualityConfig.xlsx
+++ b/Excel/EquipQualityConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t>_Id</t>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t>5,10,10</t>
+  </si>
+  <si>
+    <t>10,20,20</t>
   </si>
 </sst>
 </file>
@@ -1030,7 +1033,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:E12"/>
+  <dimension ref="C3:E13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1134,6 +1137,17 @@
       </c>
       <c r="E12" s="3" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="3:5">
+      <c r="C13" s="1">
+        <v>8</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/EquipQualityConfig.xlsx
+++ b/Excel/EquipQualityConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
   <si>
     <t>_Id</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>10,20,20</t>
+  </si>
+  <si>
+    <t>15,30,30</t>
   </si>
 </sst>
 </file>
@@ -1033,15 +1036,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:E13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
+  <dimension ref="C3:E14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="5" width="13.875" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:5">
+    <row r="3" ht="13.5" spans="3:5">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1052,7 +1055,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="3:5">
+    <row r="4" ht="13.5" spans="3:5">
       <c r="C4" s="2" t="s">
         <v>3</v>
       </c>
@@ -1063,7 +1066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="3:5">
+    <row r="5" ht="13.5" spans="3:5">
       <c r="C5" s="2" t="s">
         <v>4</v>
       </c>
@@ -1148,6 +1151,17 @@
       </c>
       <c r="E13" s="3" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="3:5">
+      <c r="C14" s="1">
+        <v>9</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/EquipQualityConfig.xlsx
+++ b/Excel/EquipQualityConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
   <si>
     <t>_Id</t>
   </si>
@@ -78,6 +78,12 @@
   </si>
   <si>
     <t>15,30,30</t>
+  </si>
+  <si>
+    <t>2001,2002,2003,2013</t>
+  </si>
+  <si>
+    <t>20,40,40,20</t>
   </si>
 </sst>
 </file>
@@ -1036,11 +1042,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:E14"/>
+  <dimension ref="C3:E15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="5" width="13.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.4166666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1077,12 +1084,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="3:3">
+    <row r="6" spans="3:5">
       <c r="C6" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="3:3">
+    <row r="7" spans="3:5">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1162,6 +1169,17 @@
       </c>
       <c r="E14" s="3" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="3:5">
+      <c r="C15" s="1">
+        <v>10</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
